--- a/Side Bar Files/GWD Data/Pump Erection .xlsx
+++ b/Side Bar Files/GWD Data/Pump Erection .xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="28">
   <si>
     <t xml:space="preserve">Pump Erection </t>
   </si>
@@ -98,34 +98,7 @@
     <t>Borewell submersible pump erection charges above 7.5 H.P.</t>
   </si>
   <si>
-    <t>Hand pump erection (deep well)</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>Say Rs 4310 x Cost Index</t>
-  </si>
-  <si>
-    <t>Hand pump erection (extra deep well)</t>
-  </si>
-  <si>
-    <t>Say Rs 5569 x Cost Index</t>
-  </si>
-  <si>
-    <t>Pulling out of hand pump for repairing and re-erecting</t>
-  </si>
-  <si>
-    <t>Say Rs 5970 x Cost Index</t>
-  </si>
-  <si>
     <t>Compressor pump fitting charge</t>
-  </si>
-  <si>
-    <t>Say Rs 3616 x Cost Index</t>
   </si>
 </sst>
 </file>
@@ -305,21 +278,29 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -379,9 +360,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -773,8 +751,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A6210EE-E866-4B07-924C-1958D540B9A6}">
-  <dimension ref="A1:F96"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{119EF408-E5ED-45F0-8232-6D61F70DB9A7}">
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:6" ht="12.75">
@@ -1576,7 +1554,9 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="12.75">
-      <c r="A55" s="22"/>
+      <c r="A55" s="22" t="s">
+        <v>15</v>
+      </c>
       <c r="B55" s="21" t="s">
         <v>16</v>
       </c>
@@ -1584,19 +1564,19 @@
         <v>17</v>
       </c>
       <c r="D55" s="23">
-        <v>0.20</v>
+        <v>0.30</v>
       </c>
       <c r="E55" s="23">
         <v>3000</v>
       </c>
       <c r="F55" s="24">
         <f>D55*E55</f>
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="12.75">
       <c r="A56" s="22" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B56" s="21" t="s">
         <v>19</v>
@@ -1605,19 +1585,19 @@
         <v>20</v>
       </c>
       <c r="D56" s="23">
-        <v>1.50</v>
+        <v>2</v>
       </c>
       <c r="E56" s="23">
         <v>784</v>
       </c>
       <c r="F56" s="24">
         <f>D56*E56</f>
-        <v>1176</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="12.75">
       <c r="A57" s="22" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B57" s="21" t="s">
         <v>22</v>
@@ -1626,27 +1606,27 @@
         <v>20</v>
       </c>
       <c r="D57" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" s="23">
         <v>645</v>
       </c>
       <c r="F57" s="24">
         <f>D57*E57</f>
-        <v>1935</v>
+        <v>645</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="12.75">
       <c r="A58" s="26"/>
       <c r="B58" s="25" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="7"/>
       <c r="F58" s="24">
         <f>SUM(F55:F57)</f>
-        <v>3711</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="12.75">
@@ -1659,7 +1639,7 @@
       <c r="E59" s="7"/>
       <c r="F59" s="24">
         <f>F58*0.01</f>
-        <v>37.11</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="12.75">
@@ -1672,7 +1652,7 @@
       <c r="E60" s="7"/>
       <c r="F60" s="24">
         <f>SUM(F58:F59)</f>
-        <v>3748.11</v>
+        <v>3144.13</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="12.75">
@@ -1685,7 +1665,7 @@
       <c r="E61" s="7"/>
       <c r="F61" s="24">
         <f>F60*0.15</f>
-        <v>562.2165</v>
+        <v>471.61950000000002</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="12.75">
@@ -1696,545 +1676,24 @@
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="7"/>
-      <c r="F62" s="24">
+      <c r="F62" s="28">
         <f>SUM(F60:F61)</f>
-        <v>4310.3265000000001</v>
+        <v>3615.7494999999999</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="12.75">
-      <c r="A63" s="26"/>
-      <c r="B63" s="28" t="s">
-        <v>30</v>
-      </c>
+      <c r="A63" s="29" t="str">
+        <f>CONCATENATE("Say Rs (",F62," x Cost Index)")</f>
+        <v>Say Rs (3615.7495 x Cost Index)</v>
+      </c>
+      <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="24"/>
-    </row>
-    <row r="64" spans="1:6" ht="12.75">
-      <c r="A64" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B64" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="7"/>
-    </row>
-    <row r="65" spans="1:6" ht="12.75">
-      <c r="A65" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="12.75">
-      <c r="A66" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" s="23">
-        <v>0.30</v>
-      </c>
-      <c r="E66" s="23">
-        <v>3000</v>
-      </c>
-      <c r="F66" s="24">
-        <f>D66*E66</f>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="12.75">
-      <c r="A67" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B67" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C67" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D67" s="23">
-        <v>2.50</v>
-      </c>
-      <c r="E67" s="23">
-        <v>784</v>
-      </c>
-      <c r="F67" s="24">
-        <f>D67*E67</f>
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="12.75">
-      <c r="A68" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C68" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D68" s="23">
-        <v>3</v>
-      </c>
-      <c r="E68" s="23">
-        <v>645</v>
-      </c>
-      <c r="F68" s="24">
-        <f>D68*E68</f>
-        <v>1935</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="12.75">
-      <c r="A69" s="26"/>
-      <c r="B69" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="24">
-        <f>SUM(F66:F68)</f>
-        <v>4795</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="12.75">
-      <c r="A70" s="26"/>
-      <c r="B70" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="24">
-        <f>F69*0.01</f>
-        <v>47.95</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="12.75">
-      <c r="A71" s="26"/>
-      <c r="B71" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="24">
-        <f>SUM(F69:F70)</f>
-        <v>4842.95</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="12.75">
-      <c r="A72" s="26"/>
-      <c r="B72" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="24">
-        <f>F71*0.15</f>
-        <v>726.4425</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="12.75">
-      <c r="A73" s="26"/>
-      <c r="B73" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="29">
-        <f>SUM(F71:F72)</f>
-        <v>5569.3924999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="12.75">
-      <c r="A74" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="7"/>
-    </row>
-    <row r="75" spans="1:6" ht="12.75">
-      <c r="A75" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B75" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="7"/>
-    </row>
-    <row r="76" spans="1:6" ht="12.75">
-      <c r="A76" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="12.75">
-      <c r="A77" s="11"/>
-      <c r="B77" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D77" s="12">
-        <v>0.20</v>
-      </c>
-      <c r="E77" s="12">
-        <v>3000</v>
-      </c>
-      <c r="F77" s="13">
-        <f>D77*E77</f>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="12.75">
-      <c r="A78" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B78" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D78" s="12">
-        <v>2.50</v>
-      </c>
-      <c r="E78" s="12">
-        <v>784</v>
-      </c>
-      <c r="F78" s="13">
-        <f>D78*E78</f>
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="12.75">
-      <c r="A79" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D79" s="12">
-        <v>4</v>
-      </c>
-      <c r="E79" s="12">
-        <v>645</v>
-      </c>
-      <c r="F79" s="13">
-        <f>D79*E79</f>
-        <v>2580</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="12.75">
-      <c r="A80" s="15"/>
-      <c r="B80" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="13">
-        <f>SUM(F77:F79)</f>
-        <v>5140</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="12.75">
-      <c r="A81" s="15"/>
-      <c r="B81" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="13">
-        <f>F80*0.01</f>
-        <v>51.40</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="12.75">
-      <c r="A82" s="15"/>
-      <c r="B82" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="13">
-        <f>SUM(F80:F81)</f>
-        <v>5191.40</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="12.75">
-      <c r="A83" s="15"/>
-      <c r="B83" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="13">
-        <f>F82*0.15</f>
-        <v>778.71</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="12.75">
-      <c r="A84" s="15"/>
-      <c r="B84" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="13">
-        <f>SUM(F82:F83)</f>
-        <v>5970.11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="12.75">
-      <c r="A85" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="7"/>
-    </row>
-    <row r="86" spans="1:6" ht="12.75">
-      <c r="A86" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B86" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="7"/>
-    </row>
-    <row r="87" spans="1:6" ht="12.75">
-      <c r="A87" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D87" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="12.75">
-      <c r="A88" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D88" s="23">
-        <v>0.30</v>
-      </c>
-      <c r="E88" s="23">
-        <v>3000</v>
-      </c>
-      <c r="F88" s="24">
-        <f>D88*E88</f>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="12.75">
-      <c r="A89" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B89" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C89" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D89" s="23">
-        <v>2</v>
-      </c>
-      <c r="E89" s="23">
-        <v>784</v>
-      </c>
-      <c r="F89" s="24">
-        <f>D89*E89</f>
-        <v>1568</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="12.75">
-      <c r="A90" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B90" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C90" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D90" s="23">
-        <v>1</v>
-      </c>
-      <c r="E90" s="23">
-        <v>645</v>
-      </c>
-      <c r="F90" s="24">
-        <f>D90*E90</f>
-        <v>645</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="12.75">
-      <c r="A91" s="26"/>
-      <c r="B91" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="24">
-        <f>SUM(F88:F90)</f>
-        <v>3113</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="12.75">
-      <c r="A92" s="26"/>
-      <c r="B92" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="24">
-        <f>F91*0.01</f>
-        <v>31.13</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="12.75">
-      <c r="A93" s="26"/>
-      <c r="B93" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="24">
-        <f>SUM(F91:F92)</f>
-        <v>3144.13</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="12.75">
-      <c r="A94" s="26"/>
-      <c r="B94" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="24">
-        <f>F93*0.15</f>
-        <v>471.61950000000002</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="12.75">
-      <c r="A95" s="26"/>
-      <c r="B95" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="29">
-        <f>SUM(F93:F94)</f>
-        <v>3615.7494999999999</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="12.75">
-      <c r="A96" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="7"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B73:E73"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="B86:F86"/>
+  <mergeCells count="41">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B6:E6"/>
@@ -2263,6 +1722,12 @@
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A63:F63"/>
     <mergeCell ref="B47:E47"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B49:E49"/>
@@ -2270,19 +1735,6 @@
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="A96:F96"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Side Bar Files/GWD Data/Pump Erection .xlsx
+++ b/Side Bar Files/GWD Data/Pump Erection .xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="28">
   <si>
     <t xml:space="preserve">Pump Erection </t>
   </si>
@@ -253,25 +253,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -370,11 +356,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -751,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{119EF408-E5ED-45F0-8232-6D61F70DB9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89BA292-0FB7-4DFD-A341-DA79651EBAA6}">
   <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -808,7 +794,9 @@
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:6" ht="12.75">
-      <c r="A5" s="11"/>
+      <c r="A5" s="11" t="s">
+        <v>1</v>
+      </c>
       <c r="B5" s="10" t="s">
         <v>10</v>
       </c>
@@ -1060,7 +1048,9 @@
       <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" ht="12.75">
-      <c r="A22" s="22"/>
+      <c r="A22" s="22" t="s">
+        <v>1</v>
+      </c>
       <c r="B22" s="21" t="s">
         <v>25</v>
       </c>
@@ -1312,7 +1302,9 @@
       <c r="F38" s="10"/>
     </row>
     <row r="39" spans="1:6" ht="12.75">
-      <c r="A39" s="11"/>
+      <c r="A39" s="11" t="s">
+        <v>1</v>
+      </c>
       <c r="B39" s="10" t="s">
         <v>25</v>
       </c>

--- a/Side Bar Files/GWD Data/Pump Erection .xlsx
+++ b/Side Bar Files/GWD Data/Pump Erection .xlsx
@@ -737,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89BA292-0FB7-4DFD-A341-DA79651EBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A5D41EC-944F-4BD7-81BD-AFBE4F4EBAA6}">
   <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Pump Erection .xlsx
+++ b/Side Bar Files/GWD Data/Pump Erection .xlsx
@@ -737,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A5D41EC-944F-4BD7-81BD-AFBE4F4EBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EFC5F6B-6C77-4867-B030-1973F991BAA6}">
   <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
